--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_47_R5.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_47_R5.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7712</v>
+        <v>2.1388</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2014</v>
+        <v>2.8043</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4302</v>
+        <v>-0.6655</v>
       </c>
       <c r="G2" t="n">
         <v>1.9388</v>
@@ -610,13 +610,13 @@
         <v>0.4639</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5979</v>
+        <v>-0.0345</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4208</v>
+        <v>0.0237</v>
       </c>
       <c r="U2" t="n">
-        <v>0.177</v>
+        <v>-0.0582</v>
       </c>
       <c r="V2" t="n">
         <v>0.9304</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6857</v>
+        <v>1.0785</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1786</v>
+        <v>3.6385</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.4928</v>
+        <v>-2.56</v>
       </c>
       <c r="G3" t="n">
         <v>4.0866</v>
@@ -688,13 +688,13 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6175</v>
+        <v>-1.2248</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8057</v>
+        <v>-0.3457</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8118</v>
+        <v>-0.879</v>
       </c>
       <c r="V3" t="n">
         <v>0.5361</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4642</v>
+        <v>1.0346</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3061</v>
+        <v>1.8093</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8419</v>
+        <v>-0.7747000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1785</v>
@@ -766,13 +766,13 @@
         <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7336</v>
+        <v>-0.1632</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3655</v>
+        <v>0.1377</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3681</v>
+        <v>-0.3009</v>
       </c>
       <c r="V4" t="n">
         <v>1.6083</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1424</v>
+        <v>0.4617</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5677</v>
+        <v>-0.0645</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4253</v>
+        <v>0.5262</v>
       </c>
       <c r="G5" t="n">
         <v>-0.8228</v>
@@ -844,13 +844,13 @@
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-0.1072</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7389</v>
+        <v>-0.2357</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0277</v>
+        <v>0.1285</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2774</v>
+        <v>-0.2101</v>
       </c>
       <c r="E6" t="n">
         <v>-0.1326</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1448</v>
+        <v>-0.0776</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0902</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1871</v>
+        <v>-0.1199</v>
       </c>
       <c r="T6" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0378</v>
+        <v>0.0294</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3757</v>
+        <v>-1.0355</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.8817</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2882</v>
+        <v>-0.1538</v>
       </c>
       <c r="G7" t="n">
         <v>0.3511</v>
@@ -1000,13 +1000,13 @@
         <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2706</v>
+        <v>-0.3892</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9085</v>
+        <v>0.1142</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6379</v>
+        <v>-0.5034</v>
       </c>
       <c r="V7" t="n">
         <v>0.3943</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2848</v>
+        <v>-1.2512</v>
       </c>
       <c r="E8" t="n">
         <v>-0.0243</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2606</v>
+        <v>-1.227</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2326</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0523</v>
+        <v>-0.0187</v>
       </c>
       <c r="T8" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>M. NOWELL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.647</v>
+        <v>-1.9848</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3055</v>
+        <v>-0.5931</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3415</v>
+        <v>-1.3917</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2923</v>
+        <v>-1.0119</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9639</v>
+        <v>-0.2724</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3284</v>
+        <v>-0.7395</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5023</v>
+        <v>0.7826</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7527</v>
+        <v>-0.1107</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.8932</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.79</v>
+        <v>-1.7944</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2112</v>
+        <v>-0.1617</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5788</v>
+        <v>-1.6327</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3412</v>
+        <v>-0.3646</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3566</v>
+        <v>-0.2159</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0154</v>
+        <v>-0.1487</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. SEDEKERSKIS</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7709</v>
+        <v>-2.4151</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8788</v>
+        <v>-2.1744</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8922</v>
+        <v>-0.2407</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2331</v>
+        <v>-2.2923</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3773</v>
+        <v>-0.9639</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.6104</v>
+        <v>-1.3284</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.081</v>
+        <v>-1.5023</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7393999999999999</v>
+        <v>-0.7527</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8204</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.1521</v>
+        <v>-0.79</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3621</v>
+        <v>-0.2112</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.79</v>
+        <v>-0.5788</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1598</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6976</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7978</v>
+        <v>0.4876</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1002</v>
+        <v>0.0854</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. NOWELL</t>
+          <t>T. SEDEKERSKIS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0264</v>
+        <v>-2.5963</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3322</v>
+        <v>-1.3009</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6941</v>
+        <v>-1.2955</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0119</v>
+        <v>-3.2331</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2724</v>
+        <v>0.3773</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7395</v>
+        <v>-3.6104</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7826</v>
+        <v>-1.081</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1107</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8932</v>
+        <v>-1.8204</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7944</v>
+        <v>-2.1521</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1617</v>
+        <v>-0.3621</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.6327</v>
+        <v>-1.79</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4062</v>
+        <v>-0.523</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.955</v>
+        <v>-0.2199</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4512</v>
+        <v>-0.3031</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.6263</v>
+        <v>-5.9566</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5429</v>
+        <v>-2.7723</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.0834</v>
+        <v>-3.1842</v>
       </c>
       <c r="G12" t="n">
         <v>-2.8241</v>
@@ -1390,13 +1390,13 @@
         <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4826</v>
+        <v>-0.8129</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0965</v>
+        <v>-0.326</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3861</v>
+        <v>-0.487</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-12.2298</v>
+        <v>-10.736</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.1854</v>
+        <v>0.3082999999999991</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.0444</v>
+        <v>-11.0445</v>
       </c>
       <c r="G13" t="n">
         <v>-5.309000000000001</v>
@@ -1441,10 +1441,10 @@
         <v>-10.49</v>
       </c>
       <c r="J13" t="n">
-        <v>8.990400000000001</v>
+        <v>8.990399999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>7.3687</v>
+        <v>7.368699999999999</v>
       </c>
       <c r="L13" t="n">
         <v>1.6216</v>
@@ -1468,10 +1468,10 @@
         <v>9.2782</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.6784</v>
+        <v>-3.1849</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.2976</v>
+        <v>-0.8041</v>
       </c>
       <c r="U13" t="n">
         <v>-2.381</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.261</v>
+        <v>5.7614</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9618</v>
+        <v>5.3157</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2992</v>
+        <v>0.4457</v>
       </c>
       <c r="G14" t="n">
         <v>3.7835</v>
@@ -1546,13 +1546,13 @@
         <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2456</v>
+        <v>0.7459</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.275</v>
+        <v>0.0788</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5206</v>
+        <v>0.6671</v>
       </c>
       <c r="V14" t="n">
         <v>0.5361</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7397</v>
+        <v>4.0638</v>
       </c>
       <c r="E15" t="n">
-        <v>3.955</v>
+        <v>4.4268</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2153</v>
+        <v>-0.363</v>
       </c>
       <c r="G15" t="n">
         <v>5.509</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2153</v>
+        <v>1.1088</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0712</v>
+        <v>0.543</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2864</v>
+        <v>0.5658</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9304</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. BROWN</t>
+          <t>I. BONGA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3782</v>
+        <v>2.5464</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4699</v>
+        <v>1.9489</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9083</v>
+        <v>0.5976</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1431</v>
+        <v>-0.8079</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3866</v>
+        <v>-2.6517</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5296</v>
+        <v>1.8438</v>
       </c>
       <c r="J16" t="n">
-        <v>1.801</v>
+        <v>0.0716</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6281</v>
+        <v>-1.2534</v>
       </c>
       <c r="L16" t="n">
-        <v>2.4291</v>
+        <v>1.325</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.658</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7584</v>
+        <v>-1.3983</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1005</v>
+        <v>0.5188</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
         <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6141</v>
+        <v>1.3544</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0633</v>
+        <v>0.8927</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.4617</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4665</v>
+        <v>1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3943</v>
+        <v>2.1444</v>
       </c>
       <c r="X16" t="n">
         <v>-1.0722</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. BONGA</t>
+          <t>S. BROWN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3448</v>
+        <v>2.1652</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4207</v>
+        <v>1.234</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0759</v>
+        <v>0.9311</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8079</v>
+        <v>1.1431</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.6517</v>
+        <v>-1.3866</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8438</v>
+        <v>2.5296</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0716</v>
+        <v>1.801</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.2534</v>
+        <v>-0.6281</v>
       </c>
       <c r="L17" t="n">
-        <v>1.325</v>
+        <v>2.4291</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8794999999999999</v>
+        <v>-0.658</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3983</v>
+        <v>-0.7584</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5188</v>
+        <v>0.1005</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1527</v>
+        <v>0.4011</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3645</v>
+        <v>-0.1727</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2117</v>
+        <v>0.5737</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0722</v>
+        <v>-1.4665</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1444</v>
+        <v>-0.3943</v>
       </c>
       <c r="X17" t="n">
         <v>-1.0722</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7207</v>
+        <v>1.9731</v>
       </c>
       <c r="E18" t="n">
-        <v>2.595</v>
+        <v>2.7129</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8742</v>
+        <v>-0.7398</v>
       </c>
       <c r="G18" t="n">
         <v>0.9195</v>
@@ -1858,13 +1858,13 @@
         <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3585</v>
+        <v>-0.1061</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3655</v>
+        <v>-0.2475</v>
       </c>
       <c r="U18" t="n">
-        <v>0.007</v>
+        <v>0.1415</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0072</v>
+        <v>1.396</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2111</v>
+        <v>-0.8573</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2183</v>
+        <v>2.2532</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4505</v>
@@ -1936,13 +1936,13 @@
         <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1356</v>
+        <v>1.5244</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0633</v>
+        <v>0.4171</v>
       </c>
       <c r="U19" t="n">
-        <v>1.0723</v>
+        <v>1.1073</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1418</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1818</v>
+        <v>0.5481</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1833</v>
+        <v>0.6551</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3651</v>
+        <v>-0.107</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2415</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.08210000000000001</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.4797</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0901</v>
+        <v>0.168</v>
       </c>
       <c r="V20" t="n">
         <v>0.1418</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6135</v>
+        <v>-0.0859</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7841</v>
+        <v>-0.5481</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1706</v>
+        <v>0.4623</v>
       </c>
       <c r="G21" t="n">
         <v>0.8250999999999999</v>
@@ -2092,13 +2092,13 @@
         <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0622</v>
+        <v>-0.5346</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8962</v>
+        <v>-0.6603</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1661</v>
+        <v>0.1256</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4267</v>
+        <v>-3.7793</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5461</v>
+        <v>-3.8436</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1194</v>
+        <v>0.0643</v>
       </c>
       <c r="G22" t="n">
         <v>-5.3712</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>3.2486</v>
+        <v>1.896</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3476</v>
+        <v>1.0501</v>
       </c>
       <c r="U22" t="n">
-        <v>0.901</v>
+        <v>0.8459</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5361</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>12.2296</v>
+        <v>14.5888</v>
       </c>
       <c r="E23" t="n">
         <v>11.0444</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1853</v>
+        <v>3.5444</v>
       </c>
       <c r="G23" t="n">
         <v>5.309100000000001</v>
@@ -2248,13 +2248,13 @@
         <v>13.9172</v>
       </c>
       <c r="S23" t="n">
-        <v>4.6785</v>
+        <v>7.0376</v>
       </c>
       <c r="T23" t="n">
-        <v>2.3811</v>
+        <v>2.3809</v>
       </c>
       <c r="U23" t="n">
-        <v>2.2975</v>
+        <v>4.6566</v>
       </c>
       <c r="V23" t="n">
         <v>-2.3969</v>
